--- a/server/assets/pet-grooming-south-india.xlsx
+++ b/server/assets/pet-grooming-south-india.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mythili\Desktop\pet-admin\server\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE113B0A-3D2B-466D-97D5-934B5507CB50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBAD5CD2-529D-4E26-ADE8-4FBDB9CF517B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
